--- a/all_models_summary.xlsx
+++ b/all_models_summary.xlsx
@@ -29,13 +29,13 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Qwen3-8B_cot_50</t>
-  </si>
-  <si>
-    <t>Qwen3-8B_cot_100</t>
-  </si>
-  <si>
-    <t>Qwen3-8B_cot_300</t>
+    <t>6a6f4aa4197940add57724a7707d069478df56b1_cot_50</t>
+  </si>
+  <si>
+    <t>6a6f4aa4197940add57724a7707d069478df56b1_cot_100</t>
+  </si>
+  <si>
+    <t>6a6f4aa4197940add57724a7707d069478df56b1_cot_300</t>
   </si>
   <si>
     <t>func_edu</t>
@@ -451,7 +451,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0.193463</v>
+        <v>0.502596</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>0.716838</v>
+        <v>0.724701</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -479,7 +479,7 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>0.681657</v>
+        <v>0.643143</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -493,7 +493,7 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0.321839</v>
+        <v>0.48044</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -507,7 +507,7 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>0.750825</v>
+        <v>0.769694</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -521,7 +521,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>0.328356</v>
+        <v>0.368641</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -535,7 +535,7 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>0.592085</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -549,7 +549,7 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>0.760231</v>
+        <v>0.686538</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -563,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>0.732584</v>
+        <v>0.729669</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -577,7 +577,7 @@
         <v>16</v>
       </c>
       <c r="D11">
-        <v>0.821963</v>
+        <v>0.719757</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -591,7 +591,7 @@
         <v>13</v>
       </c>
       <c r="D12">
-        <v>0.867428</v>
+        <v>0.847172</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -605,7 +605,7 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>0.193175</v>
+        <v>0.36682</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -619,7 +619,7 @@
         <v>11</v>
       </c>
       <c r="D14">
-        <v>0.713854</v>
+        <v>0.715994</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -633,7 +633,7 @@
         <v>12</v>
       </c>
       <c r="D15">
-        <v>0.658979</v>
+        <v>0.63976</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -647,7 +647,7 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>0.398316</v>
+        <v>0.404823</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -661,7 +661,7 @@
         <v>14</v>
       </c>
       <c r="D17">
-        <v>0.747267</v>
+        <v>0.770209</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -675,7 +675,7 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>0.368965</v>
+        <v>0.320664</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -689,7 +689,7 @@
         <v>13</v>
       </c>
       <c r="D19">
-        <v>0.57456</v>
+        <v>0.596843</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -703,7 +703,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>0.5941</v>
+        <v>0.707844</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -717,7 +717,7 @@
         <v>15</v>
       </c>
       <c r="D21">
-        <v>0.886093</v>
+        <v>0.75812</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -731,7 +731,7 @@
         <v>16</v>
       </c>
       <c r="D22">
-        <v>0.913921</v>
+        <v>0.730816</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -745,7 +745,7 @@
         <v>13</v>
       </c>
       <c r="D23">
-        <v>0.815249</v>
+        <v>0.83172</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -759,7 +759,7 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>0.27798</v>
+        <v>0.367738</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -773,7 +773,7 @@
         <v>11</v>
       </c>
       <c r="D25">
-        <v>0.729186</v>
+        <v>0.72697</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -787,7 +787,7 @@
         <v>12</v>
       </c>
       <c r="D26">
-        <v>0.748441</v>
+        <v>0.636028</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -801,7 +801,7 @@
         <v>13</v>
       </c>
       <c r="D27">
-        <v>0.558615</v>
+        <v>0.567889</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
       <c r="D28">
-        <v>0.819217</v>
+        <v>0.80868</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -829,7 +829,7 @@
         <v>10</v>
       </c>
       <c r="D29">
-        <v>0.471674</v>
+        <v>0.402616</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -843,7 +843,7 @@
         <v>13</v>
       </c>
       <c r="D30">
-        <v>0.658906</v>
+        <v>0.641398</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -857,7 +857,7 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>0.755116</v>
+        <v>0.709331</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -871,7 +871,7 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>0.9386100000000001</v>
+        <v>0.80031</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -885,7 +885,7 @@
         <v>16</v>
       </c>
       <c r="D33">
-        <v>0.904335</v>
+        <v>0.7458050000000001</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -899,7 +899,7 @@
         <v>13</v>
       </c>
       <c r="D34">
-        <v>0.859961</v>
+        <v>0.864256</v>
       </c>
     </row>
   </sheetData>
@@ -937,7 +937,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0.825534</v>
+        <v>0.752475</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -951,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>0.849252</v>
+        <v>0.777782</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -965,7 +965,7 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>0.819502</v>
+        <v>0.79084</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -979,7 +979,7 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0.830248</v>
+        <v>0.760937</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -993,7 +993,7 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>0.806768</v>
+        <v>0.66922</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1007,7 +1007,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>0.768904</v>
+        <v>0.5563630000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1021,7 +1021,7 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>0.799805</v>
+        <v>0.62304</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1035,7 +1035,7 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>0.834047</v>
+        <v>0.822287</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1049,7 +1049,7 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>0.816706</v>
+        <v>0.844449</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1063,7 +1063,7 @@
         <v>16</v>
       </c>
       <c r="D11">
-        <v>0.844715</v>
+        <v>0.820435</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1077,7 +1077,7 @@
         <v>13</v>
       </c>
       <c r="D12">
-        <v>0.859638</v>
+        <v>0.818156</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1091,7 +1091,7 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>0.825322</v>
+        <v>0.775777</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="D14">
-        <v>0.83207</v>
+        <v>0.807102</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1119,7 +1119,7 @@
         <v>12</v>
       </c>
       <c r="D15">
-        <v>0.827058</v>
+        <v>0.795825</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1133,7 +1133,7 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>0.800358</v>
+        <v>0.792452</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1147,7 +1147,7 @@
         <v>14</v>
       </c>
       <c r="D17">
-        <v>0.810171</v>
+        <v>0.662927</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1161,7 +1161,7 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>0.780232</v>
+        <v>0.567978</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
       <c r="D19">
-        <v>0.80185</v>
+        <v>0.6231179999999999</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1189,7 +1189,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>0.823165</v>
+        <v>0.816432</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1203,7 +1203,7 @@
         <v>15</v>
       </c>
       <c r="D21">
-        <v>0.734328</v>
+        <v>0.843286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1217,7 +1217,7 @@
         <v>16</v>
       </c>
       <c r="D22">
-        <v>0.794864</v>
+        <v>0.831844</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1231,7 +1231,7 @@
         <v>13</v>
       </c>
       <c r="D23">
-        <v>0.831512</v>
+        <v>0.822695</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1245,7 +1245,7 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>0.772138</v>
+        <v>0.796326</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1259,7 +1259,7 @@
         <v>11</v>
       </c>
       <c r="D25">
-        <v>0.792003</v>
+        <v>0.798325</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1273,7 +1273,7 @@
         <v>12</v>
       </c>
       <c r="D26">
-        <v>0.7828349999999999</v>
+        <v>0.805742</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1287,7 +1287,7 @@
         <v>13</v>
       </c>
       <c r="D27">
-        <v>0.6691240000000001</v>
+        <v>0.79091</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1301,7 +1301,7 @@
         <v>14</v>
       </c>
       <c r="D28">
-        <v>0.787216</v>
+        <v>0.650321</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1315,7 +1315,7 @@
         <v>10</v>
       </c>
       <c r="D29">
-        <v>0.759852</v>
+        <v>0.5687950000000001</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1329,7 +1329,7 @@
         <v>13</v>
       </c>
       <c r="D30">
-        <v>0.784327</v>
+        <v>0.62923</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1343,7 +1343,7 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>0.811429</v>
+        <v>0.815538</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1357,7 +1357,7 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>0.655492</v>
+        <v>0.840448</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1371,7 +1371,7 @@
         <v>16</v>
       </c>
       <c r="D33">
-        <v>0.736132</v>
+        <v>0.831358</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1385,7 +1385,7 @@
         <v>13</v>
       </c>
       <c r="D34">
-        <v>0.788907</v>
+        <v>0.813342</v>
       </c>
     </row>
   </sheetData>

--- a/all_models_summary.xlsx
+++ b/all_models_summary.xlsx
@@ -29,13 +29,13 @@
     <t>Value</t>
   </si>
   <si>
-    <t>6a6f4aa4197940add57724a7707d069478df56b1_cot_50</t>
-  </si>
-  <si>
-    <t>6a6f4aa4197940add57724a7707d069478df56b1_cot_100</t>
-  </si>
-  <si>
-    <t>6a6f4aa4197940add57724a7707d069478df56b1_cot_300</t>
+    <t>Qwen3-14B_cot_50</t>
+  </si>
+  <si>
+    <t>Qwen3-14B_cot_100</t>
+  </si>
+  <si>
+    <t>Qwen3-14B_cot_300</t>
   </si>
   <si>
     <t>func_edu</t>
@@ -451,7 +451,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0.502596</v>
+        <v>0.378261</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -465,7 +465,7 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>0.724701</v>
+        <v>0.692822</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -479,7 +479,7 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>0.643143</v>
+        <v>0.652688</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -493,7 +493,7 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0.48044</v>
+        <v>0.390367</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -507,7 +507,7 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>0.769694</v>
+        <v>0.7973980000000001</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -521,7 +521,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>0.368641</v>
+        <v>0.325421</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -535,7 +535,7 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>0.586</v>
+        <v>0.486464</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -549,7 +549,7 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>0.686538</v>
+        <v>0.614244</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -563,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>0.729669</v>
+        <v>0.820122</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -577,7 +577,7 @@
         <v>16</v>
       </c>
       <c r="D11">
-        <v>0.719757</v>
+        <v>0.753138</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -591,7 +591,7 @@
         <v>13</v>
       </c>
       <c r="D12">
-        <v>0.847172</v>
+        <v>0.748169</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -605,7 +605,7 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>0.36682</v>
+        <v>0.351394</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -619,7 +619,7 @@
         <v>11</v>
       </c>
       <c r="D14">
-        <v>0.715994</v>
+        <v>0.663928</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -633,7 +633,7 @@
         <v>12</v>
       </c>
       <c r="D15">
-        <v>0.63976</v>
+        <v>0.656377</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -647,7 +647,7 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>0.404823</v>
+        <v>0.367511</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -661,7 +661,7 @@
         <v>14</v>
       </c>
       <c r="D17">
-        <v>0.770209</v>
+        <v>0.790239</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -675,7 +675,7 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>0.320664</v>
+        <v>0.416021</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -689,7 +689,7 @@
         <v>13</v>
       </c>
       <c r="D19">
-        <v>0.596843</v>
+        <v>0.400453</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -703,7 +703,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>0.707844</v>
+        <v>0.447206</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -717,7 +717,7 @@
         <v>15</v>
       </c>
       <c r="D21">
-        <v>0.75812</v>
+        <v>0.908659</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -731,7 +731,7 @@
         <v>16</v>
       </c>
       <c r="D22">
-        <v>0.730816</v>
+        <v>0.787358</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -745,7 +745,7 @@
         <v>13</v>
       </c>
       <c r="D23">
-        <v>0.83172</v>
+        <v>0.7173</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -759,7 +759,7 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>0.367738</v>
+        <v>0.385449</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -773,7 +773,7 @@
         <v>11</v>
       </c>
       <c r="D25">
-        <v>0.72697</v>
+        <v>0.691892</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -787,7 +787,7 @@
         <v>12</v>
       </c>
       <c r="D26">
-        <v>0.636028</v>
+        <v>0.727746</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -801,7 +801,7 @@
         <v>13</v>
       </c>
       <c r="D27">
-        <v>0.567889</v>
+        <v>0.536068</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
       <c r="D28">
-        <v>0.80868</v>
+        <v>0.847148</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -829,7 +829,7 @@
         <v>10</v>
       </c>
       <c r="D29">
-        <v>0.402616</v>
+        <v>0.447902</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -843,7 +843,7 @@
         <v>13</v>
       </c>
       <c r="D30">
-        <v>0.641398</v>
+        <v>0.5869450000000001</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -857,7 +857,7 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>0.709331</v>
+        <v>0.70237</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -871,7 +871,7 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>0.80031</v>
+        <v>0.95592</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -885,7 +885,7 @@
         <v>16</v>
       </c>
       <c r="D33">
-        <v>0.7458050000000001</v>
+        <v>0.821872</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -899,7 +899,7 @@
         <v>13</v>
       </c>
       <c r="D34">
-        <v>0.864256</v>
+        <v>0.752049</v>
       </c>
     </row>
   </sheetData>
@@ -937,7 +937,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0.752475</v>
+        <v>0.794446</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -951,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>0.777782</v>
+        <v>0.783353</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -965,7 +965,7 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>0.79084</v>
+        <v>0.820427</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -979,7 +979,7 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0.760937</v>
+        <v>0.820074</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -993,7 +993,7 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>0.66922</v>
+        <v>0.811458</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1007,7 +1007,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>0.5563630000000001</v>
+        <v>0.776927</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1021,7 +1021,7 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>0.62304</v>
+        <v>0.807146</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1035,7 +1035,7 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>0.822287</v>
+        <v>0.852886</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1049,7 +1049,7 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>0.844449</v>
+        <v>0.8379720000000001</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1063,7 +1063,7 @@
         <v>16</v>
       </c>
       <c r="D11">
-        <v>0.820435</v>
+        <v>0.866274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1077,7 +1077,7 @@
         <v>13</v>
       </c>
       <c r="D12">
-        <v>0.818156</v>
+        <v>0.842549</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1091,7 +1091,7 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>0.775777</v>
+        <v>0.833105</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="D14">
-        <v>0.807102</v>
+        <v>0.840628</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1119,7 +1119,7 @@
         <v>12</v>
       </c>
       <c r="D15">
-        <v>0.795825</v>
+        <v>0.850665</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1133,7 +1133,7 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>0.792452</v>
+        <v>0.833998</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1147,7 +1147,7 @@
         <v>14</v>
       </c>
       <c r="D17">
-        <v>0.662927</v>
+        <v>0.827469</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1161,7 +1161,7 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>0.567978</v>
+        <v>0.806415</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
       <c r="D19">
-        <v>0.6231179999999999</v>
+        <v>0.82279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1189,7 +1189,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>0.816432</v>
+        <v>0.862877</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1203,7 +1203,7 @@
         <v>15</v>
       </c>
       <c r="D21">
-        <v>0.843286</v>
+        <v>0.869194</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1217,7 +1217,7 @@
         <v>16</v>
       </c>
       <c r="D22">
-        <v>0.831844</v>
+        <v>0.870671</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1231,7 +1231,7 @@
         <v>13</v>
       </c>
       <c r="D23">
-        <v>0.822695</v>
+        <v>0.8690290000000001</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1245,7 +1245,7 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>0.796326</v>
+        <v>0.757981</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1259,7 +1259,7 @@
         <v>11</v>
       </c>
       <c r="D25">
-        <v>0.798325</v>
+        <v>0.822112</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1273,7 +1273,7 @@
         <v>12</v>
       </c>
       <c r="D26">
-        <v>0.805742</v>
+        <v>0.816925</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1287,7 +1287,7 @@
         <v>13</v>
       </c>
       <c r="D27">
-        <v>0.79091</v>
+        <v>0.809877</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1301,7 +1301,7 @@
         <v>14</v>
       </c>
       <c r="D28">
-        <v>0.650321</v>
+        <v>0.813155</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1315,7 +1315,7 @@
         <v>10</v>
       </c>
       <c r="D29">
-        <v>0.5687950000000001</v>
+        <v>0.758772</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1329,7 +1329,7 @@
         <v>13</v>
       </c>
       <c r="D30">
-        <v>0.62923</v>
+        <v>0.7825530000000001</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1343,7 +1343,7 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>0.815538</v>
+        <v>0.861172</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1357,7 +1357,7 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>0.840448</v>
+        <v>0.847222</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1371,7 +1371,7 @@
         <v>16</v>
       </c>
       <c r="D33">
-        <v>0.831358</v>
+        <v>0.857297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1385,7 +1385,7 @@
         <v>13</v>
       </c>
       <c r="D34">
-        <v>0.813342</v>
+        <v>0.852603</v>
       </c>
     </row>
   </sheetData>
